--- a/artfynd/A 39874-2024 artfynd.xlsx
+++ b/artfynd/A 39874-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1182,6 +1182,130 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122089722</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58042</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N Bröten, Önafors, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>328479</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6487446</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ödeborg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Jihmanner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Jihmanner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39874-2024 artfynd.xlsx
+++ b/artfynd/A 39874-2024 artfynd.xlsx
@@ -1187,7 +1187,7 @@
         <v>122089722</v>
       </c>
       <c r="B6" t="n">
-        <v>58052</v>
+        <v>58057</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39874-2024 artfynd.xlsx
+++ b/artfynd/A 39874-2024 artfynd.xlsx
@@ -1202,11 +1202,6 @@
       <c r="E6" t="n">
         <v>103044</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Spinus spinus</t>
